--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-012_却下_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-012_却下_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="16859250"/>
+    <ext cx="8572500" cy="17059275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-012 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-012 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="64" customHeight="1">
+    <row r="3" ht="109" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2195,7 +2195,8 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：通知を notify 4引数・type=REQUEST_REJECTED・requestId 保存に変更、updated_at をトリガ自動更新に変更（native UPDATE の updated_at 設定と updateRequestStatus の now 引数を削除）</t>
+          <t>・確定設計変更 D1〜D10 を反映：通知を notify 4引数・type=REQUEST_REJECTED・requestId 保存に変更、updated_at をトリガ自動更新に変更（native UPDATE の updated_at 設定と updateRequestStatus の now 引数を削除）
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3730,7 +3731,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>UPDATE approval_steps SET status='REJECTED', approver_id=実行者, comment, acted_at=now(JST) WHERE id=? AND status='WAITING'（updated_at は DB トリガで自動更新）（ApprovalService#recordStep）</t>
+          <t>UPDATE approval_steps SET status='REJECTED', approver_id=実行者, comment, acted_at=now(clock) WHERE id=? AND status='WAITING'（updated_at は DB トリガで自動更新）（ApprovalService#recordStep）</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3953,7 +3954,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public ApprovalResultResponse reject(@PathVariable("id") Long id, @Valid @RequestBody(required = false) ApprovalCommentRequest request, @AuthenticationPrincipal Jwt jwt)</t>
+          <t>public ApprovalResultResponse reject(@PathVariable("id") Long id, @Valid @RequestBody(required = false) ApprovalCommentRequest request, Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -4057,17 +4058,17 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン。sub＝users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -4120,7 +4121,7 @@
           <t>1. Spring Security が Bearer トークンを検証する（無効・期限切れ → 401）
 2. @PreAuthorize でロール（ROLE_MANAGER / ROLE_ADMIN）を確認する
 3. @Valid で ApprovalCommentRequest を検証する（body 省略時は検証されない）
-4. userId = Long.valueOf(jwt.getSubject());
+4. userId = Long.valueOf(auth.getName());
 5. comment = (request == null) ? null : request.comment();
 6. return approvalService.reject(id, userId, comment);</t>
         </is>
